--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-encounter.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3526" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3850" uniqueCount="587">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -205,13 +205,209 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Encounter.implicitRules</t>
+    <t>Encounter.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Encounter.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Encounter.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Encounter.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Encounter.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Encounter.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Encounter.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Encounter.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>Encounter.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Encounter.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -222,9 +418,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Encounter.language</t>
@@ -307,38 +500,10 @@
     <t>Encounter.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.extension:estimatedDischargeDate</t>
@@ -401,26 +566,7 @@
     <t>Encounter.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Encounter.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Encounter.identifier.use</t>
@@ -472,9 +618,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-encounter-identifier-type</t>
   </si>
   <si>
@@ -688,10 +831,6 @@
     <t>Encounter.class</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Classification of patient encounter</t>
   </si>
   <si>
@@ -864,12 +1003,6 @@
     <t>inpatient | outpatient | ambulatory | emergency +.</t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
     <t>Encounter.classHistory.period</t>
   </si>
   <si>
@@ -889,9 +1022,6 @@
   </si>
   <si>
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-encounter-type</t>
@@ -2006,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN97"/>
+  <dimension ref="A1:AN106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.2265625" customWidth="true" bestFit="true"/>
@@ -2031,10 +2161,10 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="67.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="12.34765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -2409,10 +2539,10 @@
         <v>38</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>62</v>
@@ -2423,9 +2553,7 @@
       <c r="M4" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>65</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>38</v>
@@ -2474,25 +2602,25 @@
         <v>38</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AL4" t="s" s="2">
-        <v>67</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>38</v>
@@ -2503,21 +2631,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>38</v>
@@ -2564,28 +2692,28 @@
         <v>38</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>76</v>
@@ -2594,19 +2722,19 @@
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>38</v>
@@ -2617,14 +2745,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2640,19 +2768,19 @@
         <v>38</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2702,7 +2830,7 @@
         <v>38</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
@@ -2720,7 +2848,7 @@
         <v>38</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>38</v>
@@ -2731,21 +2859,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>38</v>
@@ -2754,19 +2882,19 @@
         <v>38</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2816,25 +2944,25 @@
         <v>38</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>38</v>
@@ -2845,21 +2973,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>38</v>
@@ -2868,19 +2996,19 @@
         <v>38</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2918,37 +3046,37 @@
         <v>38</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>38</v>
@@ -2959,14 +3087,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>38</v>
       </c>
@@ -2975,7 +3101,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>38</v>
@@ -2984,18 +3110,20 @@
         <v>38</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>38</v>
@@ -3032,19 +3160,19 @@
         <v>38</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -3056,13 +3184,13 @@
         <v>58</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>38</v>
@@ -3073,46 +3201,46 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>38</v>
       </c>
@@ -3121,7 +3249,7 @@
         <v>38</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>38</v>
@@ -3148,19 +3276,19 @@
         <v>38</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -3172,13 +3300,13 @@
         <v>58</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>38</v>
@@ -3189,10 +3317,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3200,7 +3328,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>37</v>
@@ -3215,15 +3343,17 @@
         <v>47</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>38</v>
@@ -3248,13 +3378,13 @@
         <v>38</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>38</v>
@@ -3287,24 +3417,24 @@
         <v>59</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3315,7 +3445,7 @@
         <v>36</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>38</v>
@@ -3324,18 +3454,20 @@
         <v>38</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>38</v>
@@ -3360,13 +3492,13 @@
         <v>38</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>38</v>
@@ -3384,71 +3516,71 @@
         <v>38</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>38</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="M13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3486,16 +3618,16 @@
         <v>38</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>128</v>
@@ -3504,19 +3636,19 @@
         <v>36</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>38</v>
@@ -3547,26 +3679,24 @@
         <v>38</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O14" t="s" s="2">
         <v>133</v>
       </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>38</v>
       </c>
@@ -3632,29 +3762,29 @@
         <v>38</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>46</v>
@@ -3666,7 +3796,7 @@
         <v>38</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>140</v>
@@ -3680,9 +3810,7 @@
       <c r="N15" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>38</v>
       </c>
@@ -3706,11 +3834,13 @@
         <v>38</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>38</v>
@@ -3728,7 +3858,7 @@
         <v>38</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
@@ -3746,32 +3876,32 @@
         <v>38</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>38</v>
@@ -3780,23 +3910,21 @@
         <v>38</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>38</v>
       </c>
@@ -3808,7 +3936,7 @@
         <v>38</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>38</v>
@@ -3844,50 +3972,50 @@
         <v>38</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>157</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>38</v>
@@ -3896,19 +4024,19 @@
         <v>38</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3922,7 +4050,7 @@
         <v>38</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>162</v>
+        <v>38</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>38</v>
@@ -3946,53 +4074,55 @@
         <v>38</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>38</v>
       </c>
@@ -4010,20 +4140,18 @@
         <v>38</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>38</v>
@@ -4072,73 +4200,75 @@
         <v>38</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>173</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>174</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>38</v>
       </c>
@@ -4174,51 +4304,51 @@
         <v>38</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>183</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4229,29 +4359,27 @@
         <v>46</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>38</v>
@@ -4276,13 +4404,13 @@
         <v>38</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>188</v>
+        <v>38</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>38</v>
@@ -4300,13 +4428,13 @@
         <v>38</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>58</v>
@@ -4315,24 +4443,24 @@
         <v>59</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4343,7 +4471,7 @@
         <v>36</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>38</v>
@@ -4355,17 +4483,15 @@
         <v>38</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>62</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>38</v>
@@ -4414,25 +4540,25 @@
         <v>38</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>65</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>38</v>
@@ -4443,21 +4569,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>38</v>
@@ -4469,15 +4595,17 @@
         <v>38</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>38</v>
@@ -4514,37 +4642,37 @@
         <v>38</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>38</v>
@@ -4555,44 +4683,46 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>38</v>
       </c>
@@ -4616,98 +4746,98 @@
         <v>38</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>38</v>
+        <v>183</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>38</v>
@@ -4732,13 +4862,11 @@
         <v>38</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>38</v>
@@ -4756,39 +4884,39 @@
         <v>38</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>38</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4808,21 +4936,23 @@
         <v>38</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>38</v>
       </c>
@@ -4834,7 +4964,7 @@
         <v>38</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>38</v>
@@ -4846,13 +4976,13 @@
         <v>38</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>188</v>
+        <v>38</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>38</v>
@@ -4870,10 +5000,10 @@
         <v>38</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>46</v>
@@ -4888,21 +5018,21 @@
         <v>38</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>38</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4922,19 +5052,19 @@
         <v>38</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4948,7 +5078,7 @@
         <v>38</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>38</v>
@@ -4984,10 +5114,10 @@
         <v>38</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>46</v>
@@ -4996,27 +5126,27 @@
         <v>58</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5024,7 +5154,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>46</v>
@@ -5039,16 +5169,16 @@
         <v>47</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5074,13 +5204,13 @@
         <v>38</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>219</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>38</v>
@@ -5098,10 +5228,10 @@
         <v>38</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>46</v>
@@ -5110,27 +5240,27 @@
         <v>58</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5150,18 +5280,20 @@
         <v>38</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>122</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>123</v>
+        <v>223</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>38</v>
@@ -5210,7 +5342,7 @@
         <v>38</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -5219,62 +5351,62 @@
         <v>46</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>67</v>
+        <v>228</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>38</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>97</v>
+        <v>233</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5300,63 +5432,63 @@
         <v>38</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>38</v>
+        <v>235</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>38</v>
+        <v>236</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>38</v>
+        <v>238</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>38</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5364,10 +5496,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>38</v>
@@ -5376,23 +5508,21 @@
         <v>38</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>38</v>
       </c>
@@ -5440,13 +5570,13 @@
         <v>38</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>58</v>
@@ -5458,21 +5588,21 @@
         <v>38</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>231</v>
+        <v>66</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>232</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5492,20 +5622,18 @@
         <v>38</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>234</v>
+        <v>63</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>38</v>
@@ -5554,7 +5682,7 @@
         <v>38</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>237</v>
+        <v>65</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -5563,41 +5691,41 @@
         <v>46</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>238</v>
+        <v>66</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>239</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>38</v>
@@ -5606,23 +5734,21 @@
         <v>38</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>69</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>241</v>
+        <v>70</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>242</v>
+        <v>71</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>38</v>
       </c>
@@ -5658,43 +5784,43 @@
         <v>38</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>245</v>
+        <v>60</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>246</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
@@ -5706,38 +5832,38 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>38</v>
+        <v>248</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>38</v>
@@ -5792,33 +5918,33 @@
         <v>36</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>252</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>253</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5826,7 +5952,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>46</v>
@@ -5838,23 +5964,21 @@
         <v>38</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>38</v>
       </c>
@@ -5878,13 +6002,13 @@
         <v>38</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>38</v>
+        <v>235</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>38</v>
@@ -5902,10 +6026,10 @@
         <v>38</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>46</v>
@@ -5920,21 +6044,21 @@
         <v>38</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>261</v>
+        <v>66</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5942,10 +6066,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>38</v>
@@ -5957,15 +6081,17 @@
         <v>38</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>38</v>
@@ -6014,39 +6140,39 @@
         <v>38</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>67</v>
+        <v>257</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>38</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6054,7 +6180,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>46</v>
@@ -6066,18 +6192,20 @@
         <v>38</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>123</v>
+        <v>260</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>38</v>
@@ -6102,13 +6230,13 @@
         <v>38</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>38</v>
+        <v>263</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>38</v>
+        <v>264</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>38</v>
@@ -6126,50 +6254,50 @@
         <v>38</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>125</v>
+        <v>259</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>46</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>67</v>
+        <v>265</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>38</v>
+        <v>266</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>38</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>38</v>
@@ -6181,17 +6309,15 @@
         <v>38</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>38</v>
@@ -6228,37 +6354,37 @@
         <v>38</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>38</v>
@@ -6269,14 +6395,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>202</v>
+        <v>68</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6289,26 +6415,24 @@
         <v>38</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>203</v>
+        <v>70</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>38</v>
       </c>
@@ -6344,19 +6468,19 @@
         <v>38</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -6368,7 +6492,7 @@
         <v>58</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>38</v>
@@ -6385,10 +6509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6408,21 +6532,23 @@
         <v>38</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>214</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>38</v>
       </c>
@@ -6446,13 +6572,13 @@
         <v>38</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>219</v>
+        <v>38</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>38</v>
@@ -6470,10 +6596,10 @@
         <v>38</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>46</v>
@@ -6488,21 +6614,21 @@
         <v>38</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6510,7 +6636,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>46</v>
@@ -6522,19 +6648,19 @@
         <v>38</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6584,10 +6710,10 @@
         <v>38</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>46</v>
@@ -6596,27 +6722,27 @@
         <v>58</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>211</v>
+        <v>283</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>212</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6624,7 +6750,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>46</v>
@@ -6639,18 +6765,20 @@
         <v>47</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>38</v>
       </c>
@@ -6674,11 +6802,13 @@
         <v>38</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>282</v>
+        <v>38</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>38</v>
@@ -6696,13 +6826,13 @@
         <v>38</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>58</v>
@@ -6711,24 +6841,24 @@
         <v>59</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>283</v>
+        <v>38</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>221</v>
+        <v>38</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6751,18 +6881,20 @@
         <v>47</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>38</v>
       </c>
@@ -6786,13 +6918,13 @@
         <v>38</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>281</v>
+        <v>38</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>291</v>
+        <v>38</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>38</v>
@@ -6810,7 +6942,7 @@
         <v>38</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -6825,24 +6957,24 @@
         <v>59</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>283</v>
+        <v>38</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6862,21 +6994,23 @@
         <v>38</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>38</v>
       </c>
@@ -6900,13 +7034,13 @@
         <v>38</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>281</v>
+        <v>38</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>296</v>
+        <v>38</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>297</v>
+        <v>38</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>38</v>
@@ -6924,7 +7058,7 @@
         <v>38</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6942,32 +7076,32 @@
         <v>38</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>299</v>
+        <v>38</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>302</v>
+        <v>38</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>38</v>
@@ -6976,20 +7110,18 @@
         <v>38</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>303</v>
+        <v>241</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>38</v>
@@ -7038,31 +7170,31 @@
         <v>38</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>307</v>
+        <v>38</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>308</v>
+        <v>66</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>309</v>
+        <v>38</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>310</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -7081,7 +7213,7 @@
         <v>36</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>38</v>
@@ -7090,20 +7222,18 @@
         <v>38</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>312</v>
+        <v>62</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>38</v>
@@ -7152,43 +7282,43 @@
         <v>38</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>311</v>
+        <v>65</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>316</v>
+        <v>38</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>317</v>
+        <v>66</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>318</v>
+        <v>38</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>319</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>321</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7207,16 +7337,16 @@
         <v>38</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>322</v>
+        <v>69</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>323</v>
+        <v>70</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>324</v>
+        <v>71</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>315</v>
+        <v>72</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7254,19 +7384,19 @@
         <v>38</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>320</v>
+        <v>76</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -7278,13 +7408,13 @@
         <v>58</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>325</v>
+        <v>38</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>326</v>
+        <v>60</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>38</v>
@@ -7295,14 +7425,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>38</v>
+        <v>248</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7315,22 +7445,26 @@
         <v>38</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>249</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>38</v>
       </c>
@@ -7378,7 +7512,7 @@
         <v>38</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>327</v>
+        <v>251</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -7390,27 +7524,27 @@
         <v>58</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>330</v>
+        <v>38</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>331</v>
+        <v>60</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>332</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7418,7 +7552,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>46</v>
@@ -7433,15 +7567,17 @@
         <v>38</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>123</v>
+        <v>315</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>38</v>
@@ -7466,13 +7602,13 @@
         <v>38</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>38</v>
+        <v>263</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>38</v>
+        <v>264</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>38</v>
@@ -7490,50 +7626,50 @@
         <v>38</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>125</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>46</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>38</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>38</v>
@@ -7545,16 +7681,16 @@
         <v>38</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>95</v>
+        <v>318</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>127</v>
+        <v>319</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7592,87 +7728,85 @@
         <v>38</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>128</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>218</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>60</v>
+        <v>257</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>38</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>203</v>
+        <v>321</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>204</v>
+        <v>322</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>38</v>
       </c>
@@ -7696,13 +7830,11 @@
         <v>38</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>38</v>
+        <v>324</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>38</v>
@@ -7720,7 +7852,7 @@
         <v>38</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>205</v>
+        <v>320</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7732,27 +7864,27 @@
         <v>58</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>38</v>
+        <v>266</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>38</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7763,7 +7895,7 @@
         <v>36</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>38</v>
@@ -7775,16 +7907,16 @@
         <v>47</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7810,13 +7942,13 @@
         <v>38</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>38</v>
@@ -7834,13 +7966,13 @@
         <v>38</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>58</v>
@@ -7849,24 +7981,24 @@
         <v>59</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7889,16 +8021,16 @@
         <v>38</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>170</v>
+        <v>331</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7924,13 +8056,13 @@
         <v>38</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>38</v>
+        <v>338</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>38</v>
+        <v>339</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>38</v>
@@ -7948,7 +8080,7 @@
         <v>38</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7960,31 +8092,31 @@
         <v>58</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>38</v>
+        <v>341</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>38</v>
+        <v>344</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8003,16 +8135,16 @@
         <v>47</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8062,7 +8194,7 @@
         <v>38</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -8074,27 +8206,27 @@
         <v>58</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8117,16 +8249,16 @@
         <v>47</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8176,7 +8308,7 @@
         <v>38</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -8188,38 +8320,38 @@
         <v>58</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>38</v>
+        <v>363</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>38</v>
@@ -8231,16 +8363,16 @@
         <v>38</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>167</v>
+        <v>364</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8290,19 +8422,19 @@
         <v>38</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>367</v>
@@ -8311,18 +8443,18 @@
         <v>368</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>369</v>
+        <v>38</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>370</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8333,7 +8465,7 @@
         <v>36</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>38</v>
@@ -8342,20 +8474,18 @@
         <v>38</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>372</v>
+        <v>241</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>38</v>
@@ -8380,13 +8510,13 @@
         <v>38</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>376</v>
+        <v>38</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>377</v>
+        <v>38</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>38</v>
@@ -8404,50 +8534,50 @@
         <v>38</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>378</v>
+        <v>59</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>382</v>
+        <v>38</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>38</v>
@@ -8456,20 +8586,18 @@
         <v>38</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>383</v>
+        <v>63</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>38</v>
@@ -8494,13 +8622,13 @@
         <v>38</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>387</v>
+        <v>38</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>38</v>
@@ -8518,43 +8646,43 @@
         <v>38</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>381</v>
+        <v>65</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>388</v>
+        <v>38</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>389</v>
+        <v>66</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>390</v>
+        <v>38</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>391</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>382</v>
+        <v>68</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8570,19 +8698,19 @@
         <v>38</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>393</v>
+        <v>69</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>394</v>
+        <v>70</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>384</v>
+        <v>71</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>385</v>
+        <v>72</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8620,19 +8748,19 @@
         <v>38</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>392</v>
+        <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
@@ -8644,31 +8772,31 @@
         <v>58</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>388</v>
+        <v>38</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>389</v>
+        <v>60</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>390</v>
+        <v>38</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>391</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>38</v>
+        <v>248</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8681,22 +8809,26 @@
         <v>38</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>396</v>
+        <v>249</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>38</v>
       </c>
@@ -8744,7 +8876,7 @@
         <v>38</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>395</v>
+        <v>251</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
@@ -8756,13 +8888,13 @@
         <v>58</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>398</v>
+        <v>60</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>38</v>
@@ -8773,10 +8905,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8787,7 +8919,7 @@
         <v>36</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>38</v>
@@ -8796,18 +8928,20 @@
         <v>38</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>122</v>
+        <v>187</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>123</v>
+        <v>379</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>38</v>
@@ -8832,13 +8966,13 @@
         <v>38</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>38</v>
+        <v>380</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>38</v>
+        <v>382</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>38</v>
@@ -8856,50 +8990,50 @@
         <v>38</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>125</v>
+        <v>378</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>38</v>
+        <v>383</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>67</v>
+        <v>384</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>38</v>
+        <v>385</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>38</v>
@@ -8911,16 +9045,16 @@
         <v>38</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>95</v>
+        <v>387</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>127</v>
+        <v>388</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8958,87 +9092,85 @@
         <v>38</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>128</v>
+        <v>386</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>218</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>60</v>
+        <v>389</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>38</v>
+        <v>390</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>94</v>
+        <v>392</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>203</v>
+        <v>393</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>204</v>
+        <v>394</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>38</v>
       </c>
@@ -9086,50 +9218,50 @@
         <v>38</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>205</v>
+        <v>391</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>38</v>
+        <v>395</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>38</v>
+        <v>397</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>38</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>38</v>
@@ -9141,16 +9273,16 @@
         <v>47</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9200,39 +9332,39 @@
         <v>38</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>390</v>
+        <v>38</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9240,7 +9372,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>46</v>
@@ -9255,16 +9387,16 @@
         <v>38</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>140</v>
+        <v>213</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>289</v>
+        <v>408</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9290,13 +9422,13 @@
         <v>38</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>413</v>
+        <v>38</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>414</v>
+        <v>38</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>38</v>
@@ -9314,7 +9446,7 @@
         <v>38</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -9326,27 +9458,27 @@
         <v>58</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>38</v>
+        <v>409</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>292</v>
+        <v>410</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>38</v>
+        <v>411</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9369,16 +9501,16 @@
         <v>38</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9404,13 +9536,13 @@
         <v>38</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>38</v>
+        <v>418</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>38</v>
+        <v>419</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>38</v>
@@ -9428,7 +9560,7 @@
         <v>38</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -9440,10 +9572,10 @@
         <v>58</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>59</v>
+        <v>420</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>38</v>
+        <v>409</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>421</v>
@@ -9452,26 +9584,26 @@
         <v>38</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>38</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>38</v>
+        <v>424</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>38</v>
@@ -9480,19 +9612,19 @@
         <v>38</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>423</v>
+        <v>187</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9518,13 +9650,13 @@
         <v>38</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>38</v>
+        <v>428</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>38</v>
+        <v>429</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>38</v>
@@ -9542,7 +9674,7 @@
         <v>38</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -9554,38 +9686,38 @@
         <v>58</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>38</v>
+        <v>430</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>38</v>
+        <v>432</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>38</v>
+        <v>433</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>38</v>
+        <v>424</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>38</v>
@@ -9594,19 +9726,19 @@
         <v>38</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>195</v>
+        <v>435</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9656,39 +9788,39 @@
         <v>38</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>38</v>
+        <v>430</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="AN67" t="s" s="2">
-        <v>38</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9699,7 +9831,7 @@
         <v>36</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>38</v>
@@ -9708,16 +9840,16 @@
         <v>38</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>123</v>
+        <v>438</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>124</v>
+        <v>439</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9768,25 +9900,25 @@
         <v>38</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>125</v>
+        <v>437</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>67</v>
+        <v>440</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>38</v>
@@ -9797,21 +9929,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>38</v>
@@ -9823,17 +9955,15 @@
         <v>38</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>38</v>
@@ -9870,37 +10000,37 @@
         <v>38</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>38</v>
@@ -9911,14 +10041,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>202</v>
+        <v>68</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9931,26 +10061,24 @@
         <v>38</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>203</v>
+        <v>70</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>38</v>
       </c>
@@ -9986,19 +10114,19 @@
         <v>38</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -10010,7 +10138,7 @@
         <v>58</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>38</v>
@@ -10027,42 +10155,46 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>38</v>
+        <v>248</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>437</v>
+        <v>249</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>38</v>
       </c>
@@ -10110,47 +10242,47 @@
         <v>38</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>436</v>
+        <v>251</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>439</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>38</v>
+        <v>445</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>46</v>
@@ -10162,18 +10294,20 @@
         <v>38</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>122</v>
+        <v>446</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>123</v>
+        <v>447</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>38</v>
@@ -10222,50 +10356,50 @@
         <v>38</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>125</v>
+        <v>444</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>46</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>38</v>
+        <v>449</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>67</v>
+        <v>450</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>38</v>
+        <v>432</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>38</v>
+        <v>451</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>38</v>
@@ -10277,16 +10411,16 @@
         <v>38</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>95</v>
+        <v>453</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>127</v>
+        <v>454</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>97</v>
+        <v>331</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10312,63 +10446,63 @@
         <v>38</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>38</v>
+        <v>455</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>38</v>
+        <v>456</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>128</v>
+        <v>452</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>60</v>
+        <v>334</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>38</v>
+        <v>457</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10385,26 +10519,24 @@
         <v>38</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>69</v>
+        <v>459</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>131</v>
+        <v>461</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>38</v>
       </c>
@@ -10428,13 +10560,13 @@
         <v>38</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>38</v>
@@ -10452,7 +10584,7 @@
         <v>38</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>137</v>
+        <v>458</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -10470,21 +10602,21 @@
         <v>38</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>138</v>
+        <v>463</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10492,7 +10624,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>46</v>
@@ -10504,23 +10636,21 @@
         <v>38</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>140</v>
+        <v>465</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>141</v>
+        <v>466</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>38</v>
       </c>
@@ -10544,11 +10674,13 @@
         <v>38</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>38</v>
@@ -10566,39 +10698,39 @@
         <v>38</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>147</v>
+        <v>464</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>138</v>
+        <v>469</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10606,7 +10738,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>46</v>
@@ -10618,35 +10750,33 @@
         <v>38</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>150</v>
+        <v>471</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>447</v>
+        <v>38</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>38</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>38</v>
@@ -10682,7 +10812,7 @@
         <v>38</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>155</v>
+        <v>470</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -10700,21 +10830,21 @@
         <v>38</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>156</v>
+        <v>474</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>157</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10722,7 +10852,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>46</v>
@@ -10734,20 +10864,18 @@
         <v>38</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>38</v>
@@ -10760,7 +10888,7 @@
         <v>38</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>162</v>
+        <v>38</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>38</v>
@@ -10796,7 +10924,7 @@
         <v>38</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -10805,41 +10933,41 @@
         <v>46</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>38</v>
@@ -10848,19 +10976,19 @@
         <v>38</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10898,85 +11026,87 @@
         <v>38</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>174</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>38</v>
+        <v>248</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>47</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>38</v>
       </c>
@@ -11024,39 +11154,39 @@
         <v>38</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>183</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11079,17 +11209,15 @@
         <v>38</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>452</v>
+        <v>167</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>38</v>
@@ -11138,7 +11266,7 @@
         <v>38</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -11150,27 +11278,27 @@
         <v>58</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>455</v>
+        <v>171</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>38</v>
+        <v>481</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11193,17 +11321,15 @@
         <v>38</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>457</v>
+        <v>63</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>38</v>
@@ -11228,13 +11354,13 @@
         <v>38</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>459</v>
+        <v>38</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>460</v>
+        <v>38</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>38</v>
@@ -11252,7 +11378,7 @@
         <v>38</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>456</v>
+        <v>65</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -11261,41 +11387,41 @@
         <v>46</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>461</v>
+        <v>66</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>462</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>38</v>
@@ -11307,16 +11433,16 @@
         <v>38</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>464</v>
+        <v>70</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>465</v>
+        <v>71</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11342,63 +11468,63 @@
         <v>38</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>281</v>
+        <v>38</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>466</v>
+        <v>38</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>467</v>
+        <v>38</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>463</v>
+        <v>76</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>292</v>
+        <v>60</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>468</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11409,31 +11535,31 @@
         <v>36</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>470</v>
+        <v>177</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>471</v>
+        <v>178</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>472</v>
+        <v>179</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>473</v>
+        <v>180</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>38</v>
@@ -11458,13 +11584,13 @@
         <v>38</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>474</v>
+        <v>182</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>475</v>
+        <v>183</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>38</v>
@@ -11482,13 +11608,13 @@
         <v>38</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>469</v>
+        <v>184</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>58</v>
@@ -11500,21 +11626,21 @@
         <v>38</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>476</v>
+        <v>185</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>477</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11522,10 +11648,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>38</v>
@@ -11534,21 +11660,23 @@
         <v>38</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>479</v>
+        <v>188</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>38</v>
       </c>
@@ -11572,13 +11700,11 @@
         <v>38</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>38</v>
@@ -11596,13 +11722,13 @@
         <v>38</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>478</v>
+        <v>193</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>58</v>
@@ -11614,21 +11740,21 @@
         <v>38</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>483</v>
+        <v>185</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>484</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11636,10 +11762,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>38</v>
@@ -11648,33 +11774,35 @@
         <v>38</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>486</v>
+        <v>196</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>38</v>
+        <v>489</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>38</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>38</v>
@@ -11686,13 +11814,13 @@
         <v>38</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>488</v>
+        <v>38</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>489</v>
+        <v>38</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>38</v>
@@ -11710,13 +11838,13 @@
         <v>38</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>485</v>
+        <v>201</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>58</v>
@@ -11728,21 +11856,21 @@
         <v>38</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>490</v>
+        <v>202</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>491</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11750,7 +11878,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>46</v>
@@ -11762,19 +11890,19 @@
         <v>38</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>452</v>
+        <v>62</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>494</v>
+        <v>206</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>315</v>
+        <v>207</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11788,7 +11916,7 @@
         <v>38</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>38</v>
@@ -11824,7 +11952,7 @@
         <v>38</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>492</v>
+        <v>209</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>36</v>
@@ -11836,27 +11964,27 @@
         <v>58</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>496</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11876,19 +12004,19 @@
         <v>38</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>140</v>
+        <v>213</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>498</v>
+        <v>214</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>499</v>
+        <v>215</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>289</v>
+        <v>216</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11914,11 +12042,13 @@
         <v>38</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>38</v>
@@ -11936,7 +12066,7 @@
         <v>38</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>497</v>
+        <v>217</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>36</v>
@@ -11948,27 +12078,27 @@
         <v>58</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>501</v>
+        <v>219</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>502</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11979,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>38</v>
@@ -11988,19 +12118,19 @@
         <v>38</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>504</v>
+        <v>223</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>505</v>
+        <v>224</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>506</v>
+        <v>225</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12050,39 +12180,39 @@
         <v>38</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>503</v>
+        <v>226</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>507</v>
+        <v>228</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>38</v>
+        <v>229</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12105,15 +12235,17 @@
         <v>38</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>122</v>
+        <v>494</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>123</v>
+        <v>495</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>38</v>
@@ -12162,7 +12294,7 @@
         <v>38</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>125</v>
+        <v>493</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -12171,16 +12303,16 @@
         <v>46</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>67</v>
+        <v>497</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>38</v>
@@ -12191,21 +12323,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>38</v>
@@ -12217,16 +12349,16 @@
         <v>38</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>95</v>
+        <v>499</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>127</v>
+        <v>500</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>97</v>
+        <v>331</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12252,99 +12384,97 @@
         <v>38</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>38</v>
+        <v>501</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>38</v>
+        <v>502</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>128</v>
+        <v>498</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>60</v>
+        <v>503</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>38</v>
+        <v>504</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>203</v>
+        <v>506</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>204</v>
+        <v>507</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>38</v>
       </c>
@@ -12368,13 +12498,13 @@
         <v>38</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>38</v>
+        <v>508</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>38</v>
+        <v>509</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>38</v>
@@ -12392,31 +12522,31 @@
         <v>38</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>205</v>
+        <v>505</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>60</v>
+        <v>334</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>38</v>
+        <v>510</v>
       </c>
     </row>
     <row r="92">
@@ -12432,10 +12562,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>38</v>
@@ -12447,18 +12577,20 @@
         <v>38</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="N92" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>38</v>
       </c>
@@ -12482,13 +12614,13 @@
         <v>38</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>38</v>
+        <v>516</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>38</v>
+        <v>517</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>38</v>
@@ -12509,36 +12641,36 @@
         <v>511</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>515</v>
+        <v>38</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>354</v>
+        <v>518</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>516</v>
+        <v>38</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12549,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>38</v>
@@ -12561,16 +12693,16 @@
         <v>38</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>521</v>
+        <v>331</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12599,10 +12731,10 @@
         <v>134</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>38</v>
@@ -12620,13 +12752,13 @@
         <v>38</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>58</v>
@@ -12638,21 +12770,21 @@
         <v>38</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>38</v>
+        <v>526</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12663,7 +12795,7 @@
         <v>36</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>38</v>
@@ -12675,16 +12807,16 @@
         <v>38</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>528</v>
+        <v>331</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12710,11 +12842,13 @@
         <v>38</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="Z94" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>38</v>
@@ -12732,13 +12866,13 @@
         <v>38</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>58</v>
@@ -12750,21 +12884,21 @@
         <v>38</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>292</v>
+        <v>532</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>415</v>
+        <v>533</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12787,16 +12921,16 @@
         <v>38</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>167</v>
+        <v>494</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>170</v>
+        <v>357</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12846,7 +12980,7 @@
         <v>38</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -12858,27 +12992,27 @@
         <v>58</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>347</v>
+        <v>537</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>212</v>
+        <v>538</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12901,16 +13035,16 @@
         <v>38</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12936,13 +13070,11 @@
         <v>38</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>38</v>
+        <v>542</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>38</v>
@@ -12960,7 +13092,7 @@
         <v>38</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>36</v>
@@ -12972,27 +13104,27 @@
         <v>58</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>353</v>
+        <v>38</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13003,7 +13135,7 @@
         <v>36</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>38</v>
@@ -13015,16 +13147,16 @@
         <v>38</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>539</v>
+        <v>241</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13074,30 +13206,1054 @@
         <v>38</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X102" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AK97" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN97" t="s" s="2">
+      <c r="Y102" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y103" s="2"/>
+      <c r="Z103" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>38</v>
       </c>
     </row>
